--- a/test.xlsx
+++ b/test.xlsx
@@ -425,18 +425,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>column_name</t>
+          <t>Column Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>data_type</t>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -451,6 +456,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,6 +469,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -475,6 +482,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -487,6 +495,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -499,6 +508,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -508,7 +518,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>double precision</t>
+          <t>float8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The geographical origin of the sample as defined by latitude. The values should be reported in decimal degrees as precise as possible (max. 8 decimal points).</t>
         </is>
       </c>
     </row>
@@ -520,9 +535,10 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>double precision</t>
-        </is>
-      </c>
+          <t>float8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,6 +551,7 @@
           <t>date</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -547,6 +564,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -559,6 +577,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -571,6 +590,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -583,6 +603,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -592,9 +613,10 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>double precision</t>
-        </is>
-      </c>
+          <t>float8</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -607,6 +629,7 @@
           <t>int4range</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -619,6 +642,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -628,9 +652,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>double precision</t>
-        </is>
-      </c>
+          <t>float8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -640,9 +665,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>double precision</t>
-        </is>
-      </c>
+          <t>float8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -655,6 +681,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -667,6 +694,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -679,6 +707,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -691,6 +720,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -703,6 +733,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -715,6 +746,7 @@
           <t>int4range</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -724,9 +756,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>double precision</t>
-        </is>
-      </c>
+          <t>float8</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -739,6 +772,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -751,6 +785,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -763,6 +798,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -775,6 +811,7 @@
           <t>date</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -787,6 +824,7 @@
           <t>date</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -799,6 +837,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -811,6 +850,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -823,6 +863,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -835,6 +876,7 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -847,11 +889,12 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>database_insert_by</t>
+          <t>Data inserter</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -859,11 +902,12 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>from_spreadsheet</t>
+          <t xml:space="preserve">External sample provider(s) email </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -871,54 +915,20 @@
           <t>text</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>database_insert_datetime_utc</t>
+          <t>Full name of external sample provider(s)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>timestamp with time zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Data inserter</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">External sample provider(s) email </t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Full name of external sample provider(s)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Is Nullable</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Example data 1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Example data 2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Example data 3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Accepted format</t>
         </is>
       </c>
     </row>
@@ -456,7 +476,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>jkl223_hollerup_20230914_1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>jkl223_hollerup_20230914_2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jkl223_hollerup_20230914_3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>&lt;ku-id&gt;_&lt;sampling_site&gt;_&lt;sampling_date&gt;_&lt;no&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -469,7 +513,15 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -482,7 +534,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -495,7 +571,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hollerup</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hollerup</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hollerup</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -508,7 +608,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Hollerup</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hollerup</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hollerup</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -518,12 +642,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>float8</t>
+          <t>double precision</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The geographical origin of the sample as defined by latitude. The values should be reported in decimal degrees as precise as possible (max. 8 decimal points).</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>61.1399</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61.1399</v>
+      </c>
+      <c r="F7" t="n">
+        <v>61.1399</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>decimal degrees, max 2 digits, max 8 decimal points (-90 to 90)</t>
         </is>
       </c>
     </row>
@@ -535,10 +673,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>float8</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>double precision</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-45.5347</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-45.5347</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-45.5347</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>decimal degrees, max 2 digits, max 8 decimal points (-180 to 180)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -551,7 +707,31 @@
           <t>date</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD or DD-MM-YYYY (choose one)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -564,7 +744,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>hlj234</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>hlj234</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hlj234; glj523</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KU Ids</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -577,7 +781,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>hlj234</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>hlj234</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hlj234</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KU Id</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -590,7 +818,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -603,7 +855,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Traversing European Coastlines</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Arctic Canada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Arctic Canada</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -613,10 +889,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>float8</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>double precision</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>300.3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Numbers (decimals allowed)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -629,7 +925,31 @@
           <t>int4range</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[10, 50)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[10, 20)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[-10, -5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Restricted mathematical notation of the form [&lt;no&gt;, &lt;no&gt;). Meaning only use "[" as the opening bracket and ")" as the closing bracket (decimals not allowed).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -642,7 +962,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>msl</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>local surface</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CGG_3_000002</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,10 +996,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>float8</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>double precision</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>200</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>300.3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Numbers (decimals allowed)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -665,10 +1029,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>float8</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>double precision</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>300.3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Numbers (decimals allowed)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -681,7 +1065,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Monolith</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OSL</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Mathematical notation: Numbers, "()", "[]" and "," (decimal allowed only if "." is used as decimal point).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -694,7 +1102,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lacustrine</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Glaciofluvial</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Glaciofluvial</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -707,7 +1139,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Outcrop</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cave</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lake</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -720,7 +1176,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5e</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>5e</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5e</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -733,7 +1213,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Holocene</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Holocene</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pleistocene</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Full names seperated by comma</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -746,7 +1250,31 @@
           <t>int4range</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[1, 105)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[1, 105)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[1, 105)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Restricted mathematical notation of the form [&lt;no&gt;, &lt;no&gt;). Meaning only use "[" as the opening bracket and ")" as the closing bracket (decimals not allowed).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -756,10 +1284,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>float8</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>double precision</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>37</v>
+      </c>
+      <c r="E25" t="n">
+        <v>37</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Number (decimal allowed)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -772,7 +1320,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Address </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -785,7 +1357,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cold room</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Walk-in Freezer</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Cold room</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -798,7 +1394,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A: shelf 4.5; W: shelf 4.6</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>A: shelf 4.5; W: shelf 4.6</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>A: shelf 4.5; W: shelf 4.6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -811,7 +1431,31 @@
           <t>date</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD or DD-MM-YYYY (choose one)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -824,7 +1468,31 @@
           <t>date</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD or DD-MM-YYYY (choose one)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -837,7 +1505,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">water content: 10 %; </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>water content: 10 %;</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>water content: 10 %; porosity: 5 %</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>&lt;measurement/observation type&gt;: &lt;measurement/observation&gt; &lt;unit (optional)&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -850,7 +1542,31 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">temperature: 7 celcius; </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">temperature: 7 celcius; </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>temperature: 7 celcius; cloud cover: overcast;</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>&lt;measurement/observation type&gt;: &lt;measurement/observation&gt; &lt;unit (optional)&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -863,7 +1579,19 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -876,7 +1604,19 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -889,7 +1629,19 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>text and/or numbers</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -902,7 +1654,15 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -915,7 +1675,15 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -928,7 +1696,15 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
